--- a/01_Agile_Planning/Hospital_Patient_System_Project_Backlog_按评价逐项修正最终版.xlsx
+++ b/01_Agile_Planning/Hospital_Patient_System_Project_Backlog_按评价逐项修正最终版.xlsx
@@ -6355,8 +6355,8 @@
       </c>
       <c r="M48" s="108" t="inlineStr">
         <is>
-          <t>In progress
-进行中</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="N48" s="237" t="inlineStr">
@@ -11680,13 +11680,13 @@
       </c>
       <c r="J26" s="148" t="inlineStr">
         <is>
-          <t>In progress
-进行中</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="K26" s="88" t="inlineStr">
         <is>
-          <t>Structural pass clean for every delivered model; the four newly found defects are either fixed or recorded in the defect log with an owner</t>
+          <t>All four defects fixed and deployed: G_RefundDecision inserted (S3), an explicit parallel gateway for urgent treatment (O1, S3), S1 branches on referralDecision from its own form, and the three worker inputs now have a form. validate-models.py and validate-form-controls.py report 0 problems.</t>
         </is>
       </c>
       <c r="L26" s="88" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="209" min="1" max="1"/>
@@ -14808,8 +14808,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="J4:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/01_Agile_Planning/Hospital_Patient_System_Project_Backlog_按评价逐项修正最终版.xlsx
+++ b/01_Agile_Planning/Hospital_Patient_System_Project_Backlog_按评价逐项修正最终版.xlsx
@@ -6203,13 +6203,13 @@
       </c>
       <c r="M46" s="108" t="inlineStr">
         <is>
-          <t>Not started
-未开始</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="N46" s="237" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Persistence delivered and verified: support/Database.java plus H2, HospitalStore and OperationsLog re-backed by tables with their public API unchanged. PersistenceCheck writes in one JVM and reads back in a second: 7 of 7 checks pass, and 41 of 41 unit tests still pass. Evidence: 05_Test_Evidence/persistence/, 08_Repository_Documents/database-integration.md</t>
         </is>
       </c>
     </row>
@@ -6279,13 +6279,13 @@
       </c>
       <c r="M47" s="108" t="inlineStr">
         <is>
-          <t>Not started
-未开始</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="N47" s="237" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>RBAC in force: the cluster had authorizations disabled and API protection skipped, so every authenticated user saw every task. Both settings corrected; 10 candidate groups and 10 role users created from the models, with group authorizations. verify-rbac.py: membership 10/10, an ungranted user sees 0 tasks where a granted role user sees 785, and each role's inbox routes only its own tasks. Evidence: 05_Test_Evidence/rbac/, 08_Repository_Documents/rbac-setup.md</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="N48" s="237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>All four open model defects fixed and deployed: the refund decision now has an exclusive gateway, the urgent-treatment AND-split is explicit, S1 branches on referralDecision from its own form, and the misplaced and missing form fields are corrected. validate-models.py and validate-form-controls.py report 0 problems. Evidence: defect-log.md group D</t>
         </is>
       </c>
     </row>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="K26" s="88" t="inlineStr">
         <is>
-          <t>All four defects fixed and deployed: G_RefundDecision inserted (S3), an explicit parallel gateway for urgent treatment (O1, S3), S1 branches on referralDecision from its own form, and the three worker inputs now have a form. validate-models.py and validate-form-controls.py report 0 problems.</t>
+          <t>All four open model defects fixed and deployed: the refund decision now has an exclusive gateway, the urgent-treatment AND-split is explicit, S1 branches on referralDecision from its own form, and the misplaced and missing form fields are corrected. validate-models.py and validate-form-controls.py report 0 problems. Evidence: defect-log.md group D</t>
         </is>
       </c>
       <c r="L26" s="88" t="inlineStr">
@@ -11744,13 +11744,13 @@
       </c>
       <c r="J27" s="148" t="inlineStr">
         <is>
-          <t>Not started
-未开始</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="K27" s="88" t="inlineStr">
         <is>
-          <t>A written schema and migration plan exists, and the second-release backlog carries the implementation as PB-45</t>
+          <t>Persistence delivered and verified: support/Database.java plus H2, HospitalStore and OperationsLog re-backed by tables with their public API unchanged. PersistenceCheck writes in one JVM and reads back in a second: 7 of 7 checks pass, and 41 of 41 unit tests still pass. Evidence: 05_Test_Evidence/persistence/, 08_Repository_Documents/database-integration.md</t>
         </is>
       </c>
       <c r="L27" s="88" t="inlineStr">
@@ -11808,13 +11808,13 @@
       </c>
       <c r="J28" s="148" t="inlineStr">
         <is>
-          <t>Not started
-未开始</t>
+          <t>Done
+完成</t>
         </is>
       </c>
       <c r="K28" s="88" t="inlineStr">
         <is>
-          <t>A group-to-permission table exists; the second-release backlog carries the implementation as PB-46; FB-11 records why it was not implemented in the initial release</t>
+          <t>RBAC in force: the cluster had authorizations disabled and API protection skipped, so every authenticated user saw every task. Both settings corrected; 10 candidate groups and 10 role users created from the models, with group authorizations. verify-rbac.py: membership 10/10, an ungranted user sees 0 tasks where a granted role user sees 785, and each role's inbox routes only its own tasks. Evidence: 05_Test_Evidence/rbac/, 08_Repository_Documents/rbac-setup.md</t>
         </is>
       </c>
       <c r="L28" s="88" t="inlineStr">
